--- a/sMSA_Supplementary_DataS1.xlsx
+++ b/sMSA_Supplementary_DataS1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q87z649\Documents\DATA\Beck, Ashley\22_MRE\suppFiles\August 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q87z649\Documents\DATA\Beck, Ashley\22_MRE\suppFiles\January 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F137273-3545-40A5-A69B-0778EB7A2A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A3EB5F-D5DA-4CB0-8056-47ADBD23FE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27135" yWindow="2595" windowWidth="25200" windowHeight="14685" xr2:uid="{A09B3D3C-DD19-460A-9609-E4EB41E96EB8}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11385" xr2:uid="{A09B3D3C-DD19-460A-9609-E4EB41E96EB8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataS1" sheetId="17" r:id="rId1"/>
@@ -566,9 +566,6 @@
       </rPr>
       <t xml:space="preserve"> K 12 strains MG1655 and NCM3722 with synthesis into consensus data sets</t>
     </r>
-  </si>
-  <si>
-    <t>Cell Geometry and Membrane Protein Crowding Constrain Growth Rate, Overflow Metabolism, Respiration, and Maintenance Energy</t>
   </si>
   <si>
     <t xml:space="preserve">literature survey, Szenk et al  </t>
@@ -879,6 +876,9 @@
       </rPr>
       <t>5</t>
     </r>
+  </si>
+  <si>
+    <t>Cell Geometry and Membrane Protein Crowding Constrain Escherichia coli Growth Rate, Overflow Metabolism, Respiration, and Maintenance Energy</t>
   </si>
 </sst>
 </file>
@@ -10941,12 +10941,12 @@
     </row>
     <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="46" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
       <c r="B7" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="55"/>
@@ -10976,7 +10976,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C10" s="55"/>
       <c r="D10" s="55"/>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" s="55"/>
       <c r="D11" s="55"/>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="55"/>
@@ -11006,7 +11006,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="55"/>
       <c r="D13" s="55"/>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="F10" s="18"/>
       <c r="G10" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
@@ -12334,7 +12334,7 @@
     </row>
     <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D72">
         <f>AVERAGE(D45:D71)</f>
@@ -12423,7 +12423,7 @@
         <v>12</v>
       </c>
       <c r="O78" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q78" s="37" t="s">
         <v>1</v>
@@ -12453,7 +12453,7 @@
         <v>12</v>
       </c>
       <c r="Z78" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AD78" t="s">
         <v>13</v>
@@ -14594,7 +14594,7 @@
     </row>
     <row r="126" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C126" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D126" s="11"/>
       <c r="E126" s="11"/>
@@ -14783,7 +14783,7 @@
     </row>
     <row r="140" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="141" spans="3:6" x14ac:dyDescent="0.25">
@@ -14830,7 +14830,7 @@
     </row>
     <row r="145" spans="1:30" x14ac:dyDescent="0.25">
       <c r="D145" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E145">
         <f>AVERAGE(E128:E144)</f>
@@ -14910,7 +14910,7 @@
         <v>12</v>
       </c>
       <c r="O149" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P149" s="28" t="s">
         <v>1</v>
@@ -14940,7 +14940,7 @@
         <v>12</v>
       </c>
       <c r="Y149" s="28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AC149" t="s">
         <v>13</v>
@@ -17174,12 +17174,12 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>141</v>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O5" s="16"/>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -17289,7 +17289,7 @@
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
@@ -17589,7 +17589,7 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
@@ -17771,7 +17771,7 @@
         <v>130</v>
       </c>
       <c r="M23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.25">
